--- a/results_(stress_test)_PCCxSigmoid-PLI-/cnn_evaluation(stress_test)_k-50_p-20_nm_basis-False_nm_modifier-False.xlsx
+++ b/results_(stress_test)_PCCxSigmoid-PLI-/cnn_evaluation(stress_test)_k-50_p-20_nm_basis-False_nm_modifier-False.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,609 +448,324 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sub6ex1</t>
+          <t>sub1ex1</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>84.01197242190676</v>
+        <v>80.47560965060251</v>
       </c>
       <c r="C2" t="n">
-        <v>83.94369956704341</v>
+        <v>80.23192314766638</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4521655129113545</v>
+        <v>0.518239580343167</v>
       </c>
       <c r="E2" t="n">
-        <v>84.01197242190676</v>
+        <v>80.47560965060252</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>sub6ex2</t>
+          <t>sub1ex2</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>78.39592037993408</v>
+        <v>78.70656320556407</v>
       </c>
       <c r="C3" t="n">
-        <v>77.88621662197723</v>
+        <v>78.41422190743202</v>
       </c>
       <c r="D3" t="n">
-        <v>0.668052239343524</v>
+        <v>0.5944895122200251</v>
       </c>
       <c r="E3" t="n">
-        <v>78.39592037993408</v>
+        <v>78.70656320556407</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>sub6ex3</t>
+          <t>sub1ex3</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>81.86221334094586</v>
+        <v>72.57311914462927</v>
       </c>
       <c r="C4" t="n">
-        <v>80.98986099175367</v>
+        <v>72.73752328061674</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4946303700407346</v>
+        <v>0.678726309724152</v>
       </c>
       <c r="E4" t="n">
-        <v>81.86221334094586</v>
+        <v>72.57311914462927</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>sub7ex1</t>
+          <t>sub2ex1</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>81.03660066263549</v>
+        <v>77.55231446638811</v>
       </c>
       <c r="C5" t="n">
-        <v>80.28262822284259</v>
+        <v>77.09558620789862</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5141996875405311</v>
+        <v>0.6505294174266358</v>
       </c>
       <c r="E5" t="n">
-        <v>81.03660066263549</v>
+        <v>77.55231446638811</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>sub7ex2</t>
+          <t>sub2ex2</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>79.98313134196663</v>
+        <v>76.04970631233834</v>
       </c>
       <c r="C6" t="n">
-        <v>79.84855570826548</v>
+        <v>75.66244660599526</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5339566177688539</v>
+        <v>0.6729300402492905</v>
       </c>
       <c r="E6" t="n">
-        <v>79.98313134196663</v>
+        <v>76.04970631233834</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>sub7ex3</t>
+          <t>sub2ex3</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>76.19849652678656</v>
+        <v>76.49607695568301</v>
       </c>
       <c r="C7" t="n">
-        <v>76.24838908704221</v>
+        <v>75.83302952541318</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6165286278973023</v>
+        <v>0.5376946692665417</v>
       </c>
       <c r="E7" t="n">
-        <v>76.19849652678656</v>
+        <v>76.49607695568301</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>sub8ex1</t>
+          <t>sub3ex1</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>84.75722108322736</v>
+        <v>71.84690178980787</v>
       </c>
       <c r="C8" t="n">
-        <v>84.65272631885709</v>
+        <v>71.81939317866127</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4083422528531325</v>
+        <v>0.7482553934057553</v>
       </c>
       <c r="E8" t="n">
-        <v>84.75722108322736</v>
+        <v>71.84690178980787</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>sub8ex2</t>
+          <t>sub3ex2</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>86.26337598076108</v>
+        <v>76.79486846772031</v>
       </c>
       <c r="C9" t="n">
-        <v>86.25727820152233</v>
+        <v>76.12072383355235</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3541962973773479</v>
+        <v>0.7068978145718574</v>
       </c>
       <c r="E9" t="n">
-        <v>86.26337598076108</v>
+        <v>76.79486846772031</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>sub8ex3</t>
+          <t>sub3ex3</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>89.55890621891191</v>
+        <v>82.50893173816382</v>
       </c>
       <c r="C10" t="n">
-        <v>89.51296611825668</v>
+        <v>82.41782171016362</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2605844371311832</v>
+        <v>0.447978958611687</v>
       </c>
       <c r="E10" t="n">
-        <v>89.55890621891193</v>
+        <v>82.50893173816382</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>sub9ex1</t>
+          <t>sub4ex1</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>86.53422607462002</v>
+        <v>75.14814141990848</v>
       </c>
       <c r="C11" t="n">
-        <v>86.41648377986373</v>
+        <v>75.02508266078999</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3934286795556545</v>
+        <v>0.7527450659622749</v>
       </c>
       <c r="E11" t="n">
-        <v>86.53422607462002</v>
+        <v>75.14814141990847</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>sub9ex2</t>
+          <t>sub4ex2</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>80.26617877317278</v>
+        <v>65.88110623794323</v>
       </c>
       <c r="C12" t="n">
-        <v>80.29752815802576</v>
+        <v>65.30778315243899</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5381122099701315</v>
+        <v>0.8656683733065924</v>
       </c>
       <c r="E12" t="n">
-        <v>80.26617877317278</v>
+        <v>65.88110623794323</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>sub9ex3</t>
+          <t>sub4ex3</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>85.41449320495852</v>
+        <v>72.72978139949308</v>
       </c>
       <c r="C13" t="n">
-        <v>84.85732810282077</v>
+        <v>72.89788271309075</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4749200362712145</v>
+        <v>0.6718244480590025</v>
       </c>
       <c r="E13" t="n">
-        <v>85.41449320495852</v>
+        <v>72.72978139949308</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>sub10ex1</t>
+          <t>sub5ex1</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>77.82679780966963</v>
+        <v>75.961470254933</v>
       </c>
       <c r="C14" t="n">
-        <v>77.49946322536429</v>
+        <v>75.16719300624642</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5939742267131806</v>
+        <v>0.6174874392027656</v>
       </c>
       <c r="E14" t="n">
-        <v>77.82679780966963</v>
+        <v>75.961470254933</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>sub10ex2</t>
+          <t>sub5ex2</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>79.80562115589235</v>
+        <v>73.86638292718796</v>
       </c>
       <c r="C15" t="n">
-        <v>79.75937217694712</v>
+        <v>73.05600659055911</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4892881041392684</v>
+        <v>0.7623208503859739</v>
       </c>
       <c r="E15" t="n">
-        <v>79.80562115589234</v>
+        <v>73.86638292718796</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>sub10ex3</t>
+          <t>sub5ex3</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>75.9085286204898</v>
+        <v>70.15735430237285</v>
       </c>
       <c r="C16" t="n">
-        <v>75.86683331866331</v>
+        <v>70.38497630426933</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6393441276003917</v>
+        <v>0.825471049391975</v>
       </c>
       <c r="E16" t="n">
-        <v>75.9085286204898</v>
+        <v>70.15735430237285</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>sub11ex1</t>
+          <t>Average</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>81.86342442408672</v>
+        <v>75.1165552181824</v>
       </c>
       <c r="C17" t="n">
-        <v>81.51863686336483</v>
+        <v>74.8114395883196</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5122846386084954</v>
+        <v>0.6700839281418464</v>
       </c>
       <c r="E17" t="n">
-        <v>81.86342442408672</v>
+        <v>75.1165552181824</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>sub11ex2</t>
+          <t>Std</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>77.98034585074265</v>
+        <v>4.023263628431949</v>
       </c>
       <c r="C18" t="n">
-        <v>77.57552159206966</v>
+        <v>3.991659000166619</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5943282381941875</v>
+        <v>0.1107755482889904</v>
       </c>
       <c r="E18" t="n">
-        <v>77.98034585074265</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>sub11ex3</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>86.34391300962811</v>
-      </c>
-      <c r="C19" t="n">
-        <v>86.36752873968072</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0.3686665125812094</v>
-      </c>
-      <c r="E19" t="n">
-        <v>86.34391300962811</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>sub12ex1</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>79.14661891538853</v>
-      </c>
-      <c r="C20" t="n">
-        <v>78.93173168610736</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0.5424022022634745</v>
-      </c>
-      <c r="E20" t="n">
-        <v>79.14661891538854</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>sub12ex2</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>69.10111679166775</v>
-      </c>
-      <c r="C21" t="n">
-        <v>68.65415649220166</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0.7843680878480275</v>
-      </c>
-      <c r="E21" t="n">
-        <v>69.10111679166775</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>sub12ex3</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>81.97899635809998</v>
-      </c>
-      <c r="C22" t="n">
-        <v>81.3310776779546</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0.5110588565624009</v>
-      </c>
-      <c r="E22" t="n">
-        <v>81.97899635809998</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>sub13ex1</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>77.09210287286223</v>
-      </c>
-      <c r="C23" t="n">
-        <v>76.99769537996862</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0.6345007189239065</v>
-      </c>
-      <c r="E23" t="n">
-        <v>77.09210287286223</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>sub13ex2</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>82.75201342572169</v>
-      </c>
-      <c r="C24" t="n">
-        <v>82.40732682261194</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0.4580686705807845</v>
-      </c>
-      <c r="E24" t="n">
-        <v>82.75201342572167</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>sub13ex3</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>79.95328679313835</v>
-      </c>
-      <c r="C25" t="n">
-        <v>79.58651315552537</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0.5095133395399898</v>
-      </c>
-      <c r="E25" t="n">
-        <v>79.95328679313835</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>sub14ex1</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>81.24533949255616</v>
-      </c>
-      <c r="C26" t="n">
-        <v>80.88806708177756</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0.5156408101320267</v>
-      </c>
-      <c r="E26" t="n">
-        <v>81.24533949255616</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>sub14ex2</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>74.40548793674687</v>
-      </c>
-      <c r="C27" t="n">
-        <v>74.23160093580339</v>
-      </c>
-      <c r="D27" t="n">
-        <v>0.6760270526399836</v>
-      </c>
-      <c r="E27" t="n">
-        <v>74.40548793674685</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>sub14ex3</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>79.58788570835388</v>
-      </c>
-      <c r="C28" t="n">
-        <v>79.44039629937672</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0.5650780002276103</v>
-      </c>
-      <c r="E28" t="n">
-        <v>79.58788570835387</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>sub15ex1</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>89.17905864237579</v>
-      </c>
-      <c r="C29" t="n">
-        <v>89.3096307773929</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0.3046090570899347</v>
-      </c>
-      <c r="E29" t="n">
-        <v>89.17905864237579</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>sub15ex2</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>90.21116099620238</v>
-      </c>
-      <c r="C30" t="n">
-        <v>90.26003962003335</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0.2753416570446764</v>
-      </c>
-      <c r="E30" t="n">
-        <v>90.21116099620238</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>sub15ex3</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>90.50216697376274</v>
-      </c>
-      <c r="C31" t="n">
-        <v>89.70506014693856</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0.3120939080060149</v>
-      </c>
-      <c r="E31" t="n">
-        <v>90.50216697376274</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>81.63888672624043</v>
-      </c>
-      <c r="C32" t="n">
-        <v>81.38414376233509</v>
-      </c>
-      <c r="D32" t="n">
-        <v>0.4998568392452176</v>
-      </c>
-      <c r="E32" t="n">
-        <v>81.63888672624043</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Std</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>4.909171709155069</v>
-      </c>
-      <c r="C33" t="n">
-        <v>4.943347228376327</v>
-      </c>
-      <c r="D33" t="n">
-        <v>0.1241930907813552</v>
-      </c>
-      <c r="E33" t="n">
-        <v>4.90917170915507</v>
+        <v>4.023263628431951</v>
       </c>
     </row>
   </sheetData>
@@ -1096,16 +811,16 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>81.63888672624043</v>
+        <v>75.1165552181824</v>
       </c>
       <c r="B2" t="n">
-        <v>81.38414376233509</v>
+        <v>74.8114395883196</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4998568392452176</v>
+        <v>0.6700839281418464</v>
       </c>
       <c r="D2" t="n">
-        <v>81.63888672624043</v>
+        <v>75.1165552181824</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1115,16 +830,16 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>4.909171709155069</v>
+        <v>4.023263628431949</v>
       </c>
       <c r="B3" t="n">
-        <v>4.943347228376327</v>
+        <v>3.991659000166619</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1241930907813552</v>
+        <v>0.1107755482889904</v>
       </c>
       <c r="D3" t="n">
-        <v>4.90917170915507</v>
+        <v>4.023263628431951</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1190,28 +905,28 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>81.63888672624043</v>
+        <v>75.1165552181824</v>
       </c>
       <c r="B2" t="n">
-        <v>4.909171709155069</v>
+        <v>4.023263628431949</v>
       </c>
       <c r="C2" t="n">
-        <v>81.38414376233509</v>
+        <v>74.8114395883196</v>
       </c>
       <c r="D2" t="n">
-        <v>4.943347228376327</v>
+        <v>3.991659000166619</v>
       </c>
       <c r="E2" t="n">
-        <v>81.63888672624043</v>
+        <v>75.1165552181824</v>
       </c>
       <c r="F2" t="n">
-        <v>4.90917170915507</v>
+        <v>4.023263628431951</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4998568392452176</v>
+        <v>0.6700839281418464</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1241930907813552</v>
+        <v>0.1107755482889904</v>
       </c>
     </row>
   </sheetData>
